--- a/Dokumentáció/Osztalydiagram.xlsx
+++ b/Dokumentáció/Osztalydiagram.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/woynarovichgergely/NagyHF2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/woynarovichgergely/NagyHF2/Dokumentáció/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A10ED83-70F9-4D4B-977C-067C4BEF1847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CECA67-FF74-FF4D-A1A9-2E6B16DAD27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16860" xr2:uid="{A51E72F9-05D7-2C46-AF49-BC41CBEC95B4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Node</t>
   </si>
@@ -140,13 +140,37 @@
     <t>#operator&lt;&lt;(ostream&amp;: os, Node&amp;: n): ostream&amp;</t>
   </si>
   <si>
-    <t>#operator&lt;&lt;(ostream&amp;: os, Edge&amp;: e): ostream&amp;</t>
-  </si>
-  <si>
     <t>#listNodes(ostream&amp; os): void</t>
   </si>
   <si>
     <t>#printRoute(Node[*]: path): void</t>
+  </si>
+  <si>
+    <t>#operator==(const Node&amp; other) const</t>
+  </si>
+  <si>
+    <t>#getId(): int</t>
+  </si>
+  <si>
+    <t>#friend operator&lt;&lt;(ostream&amp;: os, Edge&amp;: e): ostream&amp;</t>
+  </si>
+  <si>
+    <t>#Edge()</t>
+  </si>
+  <si>
+    <t>#getNodes(): Node[*]</t>
+  </si>
+  <si>
+    <t>#findNodebyname(String): Node</t>
+  </si>
+  <si>
+    <t>#virtual ~Graph()</t>
+  </si>
+  <si>
+    <t>#Planner()</t>
+  </si>
+  <si>
+    <t>#routePlanner(String startName, String endName,) : void</t>
   </si>
 </sst>
 </file>
@@ -183,7 +207,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -232,17 +256,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -251,11 +264,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -271,6 +284,362 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>172720</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>111760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>719156</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>122410</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBE2133F-DF96-B803-B040-D646EF7C5F32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="7975600" y="2346960"/>
+          <a:ext cx="4000836" cy="10650"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1798320</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>71120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1798320</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9180DFF-ECF8-1E60-BAB2-51EBEBFD67DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13878560" y="3525520"/>
+          <a:ext cx="0" cy="975360"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1473200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1190625</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{727BD36F-2685-C2FD-C8D9-FA69C595398B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2300968" y="3605893"/>
+          <a:ext cx="2699657" cy="1006384"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2743200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1767840</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Straight Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29CAA774-F356-CB4B-9FBD-C99E443390B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="6553200" y="3545840"/>
+          <a:ext cx="3017520" cy="1046480"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150">
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1054054</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>55291</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1226774</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>14650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rectangle 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14008513-83F7-623A-B47E-7751B2252DA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4864054" y="3525112"/>
+          <a:ext cx="172720" cy="163467"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2720249</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>37601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2892969</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>201068</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A9083E5-6005-D04E-B77F-59999EDBFCCA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6530249" y="3507422"/>
+          <a:ext cx="172720" cy="163467"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,149 +959,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22717E9E-34C8-F641-A66E-EBF1E637C5D3}">
-  <dimension ref="B6:K15"/>
+  <dimension ref="B7:F35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39.1640625" customWidth="1"/>
-    <col min="4" max="4" width="39.83203125" customWidth="1"/>
-    <col min="7" max="7" width="51.1640625" customWidth="1"/>
-    <col min="9" max="9" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" customWidth="1"/>
     <col min="11" max="11" width="35.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="4" t="s">
+    <row r="7" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.2">
+      <c r="C16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B24" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="1" t="s">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B25" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D25" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="s">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B26" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B27" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B28" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D29" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="2" t="s">
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D30" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B31" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D32" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D33" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D34" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="D14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="D15" s="2" t="s">
-        <v>34</v>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D35" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="27" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>